--- a/AAII_Financials/Quarterly/FG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>FG</t>
   </si>
@@ -656,186 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1187000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1765000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1694000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1364000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>908000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1559000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1444000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1172000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1569000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1616000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>855000</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1149000</v>
+      </c>
+      <c r="E9" s="3">
         <v>484000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1265000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1181000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>993000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>524000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>927000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1095000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>608000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1161000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1632000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>292000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>272000</v>
+      </c>
+      <c r="E10" s="3">
         <v>703000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>513000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>371000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>384000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>632000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>349000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>564000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>408000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-16000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>563000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,46 +983,52 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E15" s="3">
         <v>173000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>174000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>180000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>158000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>153000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>152000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>147000</v>
       </c>
       <c r="K15" s="3">
         <v>147000</v>
       </c>
       <c r="L15" s="3">
+        <v>147000</v>
+      </c>
+      <c r="M15" s="3">
         <v>123000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>110000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1040,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="E17" s="3">
         <v>823000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1563000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1521000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1266000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>894000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1109000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1438000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>890000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1397000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1965000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E18" s="3">
         <v>364000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>202000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>173000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>98000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>450000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>282000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>172000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-349000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>404000</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1145,46 +1178,52 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E21" s="3">
         <v>537000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>376000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>353000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>256000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>167000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>602000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>153000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>429000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>295000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-239000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1195,110 +1234,119 @@
         <v>41000</v>
       </c>
       <c r="F22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="G22" s="3">
         <v>42000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>41000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>30000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="E23" s="3">
         <v>323000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>161000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>131000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>412000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>254000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>142000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-375000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>380000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E24" s="3">
         <v>74000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>85000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-25000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>50000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-76000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E26" s="3">
         <v>249000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>130000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>120000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>42000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>327000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>204000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>116000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-299000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>306000</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E27" s="3">
         <v>244000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>124000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>114000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>323000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>198000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>111000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-299000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>306000</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1601,46 +1670,52 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E33" s="3">
         <v>248000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>128000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>118000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>327000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>203000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>115000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-299000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>306000</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E35" s="3">
         <v>248000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>128000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>118000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>327000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>203000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>115000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-299000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>306000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,122 +1875,132 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1324000</v>
+        <v>2098000</v>
       </c>
       <c r="E41" s="3">
+        <v>1318000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1486000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2189000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1884000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3293000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2264000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3539000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3526000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2372000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1563000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1742000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1036000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1129000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1000000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>851000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>589000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2426000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>681000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>421000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>263000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1509000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>168000</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E43" s="3">
         <v>78000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>83000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>67000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>27000</v>
       </c>
       <c r="N43" s="3">
         <v>27000</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,122 +2037,134 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23000000</v>
+      </c>
+      <c r="E45" s="3">
         <v>21475000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18648000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18566000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17188000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15987000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14177000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14370000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12761000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11812000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10349000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8686000</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25752000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24404000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22374000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22132000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20196000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20266000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19806000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18869000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16919000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14470000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13758000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10623000</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>58895000</v>
+      </c>
+      <c r="E47" s="3">
         <v>58806000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>58924000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>57829000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>55944000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52905000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50845000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>51685000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48669000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47043000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44605000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41019000</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2094,46 +2201,52 @@
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8660000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8530000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8455000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8277000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8122000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7900000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7751000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7528000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6969000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6629000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5956000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5754000</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2324,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E52" s="3">
         <v>308000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>285000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>242000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>213000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>187000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>189000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>134000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>103000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>429000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>88000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>413000</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2406,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>103592000</v>
+      </c>
+      <c r="E54" s="3">
         <v>101031000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>98430000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96137000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>91816000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88007000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84931000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84123000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78512000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74434000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70202000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63623000</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,236 +2483,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17770000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16849000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14490000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13918000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12737000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11757000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11007000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10260000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8936000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8294000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7472000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6335000</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>10000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>358000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>385000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>376000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>362000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9146000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7987000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8510000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8018000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7661000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6959000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6763000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7986000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6504000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6280000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5502000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4491000</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27372000</v>
+      </c>
+      <c r="E60" s="3">
         <v>25223000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23424000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22353000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20755000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19072000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18192000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19030000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16183000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15287000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13703000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11114000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2250000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2249000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2247000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>2244000</v>
       </c>
       <c r="G61" s="3">
         <v>2244000</v>
       </c>
       <c r="H61" s="3">
+        <v>2244000</v>
+      </c>
+      <c r="I61" s="3">
         <v>2243000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2181000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1690000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1692000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1402000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1403000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1581000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>69276000</v>
+      </c>
+      <c r="E62" s="3">
         <v>68810000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>67842000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66600000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64260000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>62207000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>60482000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>58928000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>56849000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54062000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51993000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48556000</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2850,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>98898000</v>
+      </c>
+      <c r="E66" s="3">
         <v>96282000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93513000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91197000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87259000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83522000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80855000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>79648000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74724000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>70751000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67099000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61251000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3072,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2665000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2778000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2568000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2478000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2394000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2389000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2440000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2145000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2182000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2011000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1926000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2252000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3236,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4609000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4639000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4804000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4824000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4438000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4363000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3951000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4346000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3654000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3546000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3103000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2372000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E81" s="3">
         <v>248000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>128000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>118000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>327000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>203000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>115000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-299000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>306000</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3424,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="E83" s="3">
         <v>19000</v>
       </c>
       <c r="F83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="G83" s="3">
         <v>21000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>8000</v>
       </c>
       <c r="M83" s="3">
         <v>8000</v>
       </c>
       <c r="N83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O83" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="E89" s="3">
         <v>743000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1168000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>937000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1620000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>956000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1320000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2090000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1055000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1534000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2222000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>795000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3728,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3518,37 +3738,40 @@
         <v>-2000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="F91" s="3">
         <v>-3000</v>
       </c>
       <c r="G91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-5000</v>
       </c>
       <c r="I91" s="3">
         <v>-5000</v>
       </c>
       <c r="J91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-7000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-939000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2287000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1869000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3464000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-809000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2808000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1916000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1845000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1384000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3264000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1408000</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,46 +3909,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E96" s="3">
         <v>38000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>39000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>33000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>35000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>30000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>33000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>31000</v>
       </c>
       <c r="K96" s="3">
         <v>31000</v>
       </c>
       <c r="L96" s="3">
-        <v>26000</v>
+        <v>31000</v>
       </c>
       <c r="M96" s="3">
         <v>26000</v>
       </c>
       <c r="N96" s="3">
+        <v>26000</v>
+      </c>
+      <c r="O96" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-816000</v>
+      </c>
+      <c r="E100" s="3">
         <v>34000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>416000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1237000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>435000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>882000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>213000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-161000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1944000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>659000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>863000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>667000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4153,48 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-162000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-703000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>305000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1409000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1029000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1275000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1154000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>809000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-179000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>54000</v>
       </c>
     </row>
